--- a/data/TOTO_Playoffs.xlsx
+++ b/data/TOTO_Playoffs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/toto-wm2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{A299B5FB-7316-45B5-8838-E7E2A244E032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1F5C8D2-1ABC-BF45-A496-EE8BDB89CEBE}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{A299B5FB-7316-45B5-8838-E7E2A244E032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE3B34FC-E889-2D4E-8B04-22E1E06D2790}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{273D125B-E266-46F2-82F7-47D58BEE0A24}"/>
   </bookViews>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="71">
   <si>
     <t>Achtelfinale 1</t>
   </si>
@@ -1637,8 +1637,12 @@
       </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
+      <c r="N14" s="4">
+        <v>1</v>
+      </c>
+      <c r="O14" s="4">
+        <v>4</v>
+      </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="4">
@@ -1657,12 +1661,20 @@
       </c>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="Z14" s="4">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="4">
+        <v>2</v>
+      </c>
       <c r="AB14" s="2"/>
       <c r="AC14" s="2"/>
-      <c r="AD14" s="4"/>
-      <c r="AE14" s="4"/>
+      <c r="AD14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="4">
+        <v>0</v>
+      </c>
       <c r="AF14" s="2"/>
     </row>
     <row r="15" spans="1:32" ht="17.25" x14ac:dyDescent="0.3">
@@ -1690,7 +1702,7 @@
       <c r="M15" s="2"/>
       <c r="N15" s="15" t="str">
         <f>IF(N14=O14,"",IF(N14&gt;O14,N13,O13))</f>
-        <v/>
+        <v>Belgien</v>
       </c>
       <c r="O15" s="15"/>
       <c r="P15" s="2"/>
@@ -1711,14 +1723,13 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="15" t="str">
         <f>IF(Z14=AA14,"",IF(Z14&gt;AA14,Z13,AA13))</f>
-        <v/>
+        <v>Argentinien</v>
       </c>
       <c r="AA15" s="15"/>
       <c r="AB15" s="2"/>
       <c r="AC15" s="2"/>
-      <c r="AD15" s="15" t="str">
-        <f>IF(AD14=AE14,"",IF(AD14&gt;AE14,AD13,AE13))</f>
-        <v/>
+      <c r="AD15" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="AE15" s="15"/>
       <c r="AF15" s="2"/>
@@ -1823,7 +1834,7 @@
       </c>
       <c r="M18" s="3" t="str">
         <f>N15</f>
-        <v/>
+        <v>Belgien</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -1846,11 +1857,11 @@
       <c r="AA18" s="2"/>
       <c r="AB18" s="3" t="str">
         <f>Z15</f>
-        <v/>
+        <v>Argentinien</v>
       </c>
       <c r="AC18" s="3" t="str">
         <f>AD15</f>
-        <v/>
+        <v>Schweiz</v>
       </c>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>

--- a/data/TOTO_Playoffs.xlsx
+++ b/data/TOTO_Playoffs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3986c3747c471c36/Dokumente/Coding Projekte/toto-wm2026/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{A299B5FB-7316-45B5-8838-E7E2A244E032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D328BEC6-DD28-4846-8D0F-A880828AD5AA}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{A299B5FB-7316-45B5-8838-E7E2A244E032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{027C67B9-6AA6-4146-943A-BAF718D803CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{273D125B-E266-46F2-82F7-47D58BEE0A24}"/>
   </bookViews>
@@ -2108,8 +2108,12 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
+      <c r="P24" s="4">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>6</v>
+      </c>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
@@ -2151,7 +2155,7 @@
       <c r="O25" s="2"/>
       <c r="P25" s="17" t="str">
         <f>IF(P24=Q24,"",IF(P24&gt;Q24,P23,Q23))</f>
-        <v/>
+        <v>England</v>
       </c>
       <c r="Q25" s="17"/>
       <c r="R25" s="2"/>
@@ -2299,8 +2303,12 @@
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
+      <c r="P29" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>0</v>
+      </c>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
@@ -2335,7 +2343,7 @@
       <c r="O30" s="2"/>
       <c r="P30" s="17" t="str">
         <f>IF(P29=Q29,"",IF(P29&gt;Q29,P28,Q28))</f>
-        <v/>
+        <v>Spanien</v>
       </c>
       <c r="Q30" s="17"/>
       <c r="R30" s="2"/>
